--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M409"/>
+  <dimension ref="A1:M410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12277,7 +12277,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1057472-14046-CM26</t>
+          <t>1381-768-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12302,41 +12302,37 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.980.320-5</t>
+          <t>61.602.245-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE GORBEA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.943.080-6</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1732.91</v>
+        <v>985.17</v>
       </c>
     </row>
     <row r="186">
@@ -12663,7 +12659,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1381-768-CM26</t>
+          <t>1057472-14046-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12688,37 +12684,41 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.602.245-8</t>
+          <t>61.980.320-5</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE GORBEA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>77.305.910-1</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>985.17</v>
+        <v>1732.91</v>
       </c>
     </row>
     <row r="192">
@@ -12984,7 +12984,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>855-212-CM26</t>
+          <t>4596-960-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13009,37 +13009,41 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>9149.43</v>
+        <v>795.75</v>
       </c>
     </row>
     <row r="197">
@@ -13305,7 +13309,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4596-960-CM26</t>
+          <t>855-212-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13330,41 +13334,37 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>795.75</v>
+        <v>9149.43</v>
       </c>
     </row>
     <row r="202">
@@ -19290,7 +19290,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4891-58-CM26</t>
+          <t>2656-1219-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19310,52 +19310,48 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.978.780-3</t>
+          <t>69.150.100-0</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1356.14</v>
+        <v>8264.6</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2656-1219-CM26</t>
+          <t>4891-58-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19375,42 +19371,46 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.150.100-0</t>
+          <t>61.978.780-3</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>8264.6</v>
+        <v>1356.14</v>
       </c>
     </row>
     <row r="296">
@@ -20050,7 +20050,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1057461-1723-CM26</t>
+          <t>3477-726-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20070,37 +20070,37 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA KIMUN SPA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.725.256-9</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1433.3</v>
+        <v>14545.15</v>
       </c>
     </row>
     <row r="307">
@@ -20310,7 +20310,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1605-225-CM26</t>
+          <t>229-767-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20335,41 +20335,37 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5238.92</v>
+        <v>1146.54</v>
       </c>
     </row>
     <row r="311">
@@ -20505,7 +20501,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>229-767-CM26</t>
+          <t>1605-225-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20530,37 +20526,41 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
+          <t>77.305.910-1</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1146.54</v>
+        <v>5238.92</v>
       </c>
     </row>
     <row r="314">
@@ -20696,7 +20696,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3477-726-CM26</t>
+          <t>1057461-1723-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20716,37 +20716,37 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA KIMUN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.725.256-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20755,7 +20755,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>14545.15</v>
+        <v>1433.3</v>
       </c>
     </row>
     <row r="317">
@@ -21346,7 +21346,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2180-201-CM26</t>
+          <t>1301883-288-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21371,27 +21371,27 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -21405,7 +21405,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>799.97</v>
+        <v>1620.82</v>
       </c>
     </row>
     <row r="327">
@@ -21476,7 +21476,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>791766-94-CM26</t>
+          <t>2180-201-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21501,27 +21501,27 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -21535,13 +21535,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>7118.19</v>
+        <v>799.97</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>630-225-CM26</t>
+          <t>791766-94-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21566,12 +21566,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.501.000-6</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL TRABAJO</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21581,12 +21581,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -21600,13 +21600,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1539.74</v>
+        <v>7118.19</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>607-334-CM26</t>
+          <t>630-225-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21631,12 +21631,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.809.000-0</t>
+          <t>61.501.000-6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>PARQUE METROPOLITANO DE SANTIAGO</t>
+          <t>SUBSECRETARIA DEL TRABAJO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21646,17 +21646,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21665,13 +21665,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>5062.58</v>
+        <v>1539.74</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>3047-562-CM26</t>
+          <t>607-334-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21696,32 +21696,32 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.809.000-0</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>PARQUE METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DISTRIBUCION GLOBAL LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.100.732-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21730,13 +21730,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>775.23</v>
+        <v>5062.58</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5060-814-CM26</t>
+          <t>3047-562-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21761,32 +21761,32 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL DISTRIBUCION GLOBAL LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.100.732-7</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -21795,13 +21795,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>7038.1</v>
+        <v>775.23</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1658-2646-CM26</t>
+          <t>5060-814-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21841,17 +21841,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA KIMUN SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.725.256-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21860,13 +21860,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>14407.79</v>
+        <v>7038.1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2111-13081-CM26</t>
+          <t>1658-2646-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21886,37 +21886,37 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA KIMUN SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.725.256-9</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21925,13 +21925,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>3386.82</v>
+        <v>14407.79</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3152-531-CM26</t>
+          <t>2111-13081-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21946,42 +21946,42 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -21990,13 +21990,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1282.16</v>
+        <v>3386.82</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2395-1010-CM26</t>
+          <t>3152-531-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22021,32 +22021,32 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.254.900-7</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -22055,13 +22055,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1839.73</v>
+        <v>1282.16</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1272223-98-CM26</t>
+          <t>2395-1010-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22086,12 +22086,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>65.020.108-6</t>
+          <t>69.254.900-7</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22120,13 +22120,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>779.42</v>
+        <v>1839.73</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1715-94-CM26</t>
+          <t>1272223-98-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22151,43 +22151,47 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>65.020.108-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>764.98</v>
+        <v>779.42</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1272228-27-CM26</t>
+          <t>1715-94-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22212,41 +22216,37 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>65.020.633-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>862.4400000000001</v>
+        <v>764.98</v>
       </c>
     </row>
     <row r="340">
@@ -22317,7 +22317,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2827-724-CM26</t>
+          <t>3674-660-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22342,32 +22342,32 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22376,13 +22376,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2387.61</v>
+        <v>1209.77</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5413-1163-CM26</t>
+          <t>2827-724-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22407,17 +22407,17 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -22441,13 +22441,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2245.33</v>
+        <v>2387.61</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1126922-1580-CM26</t>
+          <t>5413-1163-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22472,12 +22472,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22487,17 +22487,17 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -22506,13 +22506,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2198.77</v>
+        <v>2245.33</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1057389-4614-CM26</t>
+          <t>1126922-1580-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22532,32 +22532,32 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -22571,13 +22571,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1853.31</v>
+        <v>2198.77</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>792906-17-CM26</t>
+          <t>1057389-4614-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22597,22 +22597,22 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.980.220-9</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -22636,13 +22636,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>767.11</v>
+        <v>1853.31</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4487-400-CM26</t>
+          <t>792906-17-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22667,12 +22667,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.170.801-2</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22682,28 +22682,32 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1231.73</v>
+        <v>767.11</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1057379-550-CM26</t>
+          <t>4487-400-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22728,47 +22732,43 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>69.170.801-2</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>753.0599999999999</v>
+        <v>1231.73</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2789-593-CM26</t>
+          <t>1057379-550-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22793,43 +22793,47 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>887.05</v>
+        <v>753.0599999999999</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>4104-227-CM26</t>
+          <t>2789-593-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22854,47 +22858,43 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.191.200-0</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Municipalidad de Gorbea</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>764.76</v>
+        <v>887.05</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2107-2256-CM26</t>
+          <t>4104-227-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22919,17 +22919,17 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>69.191.200-0</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22953,13 +22953,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1876.12</v>
+        <v>764.76</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3674-660-CM26</t>
+          <t>2107-2256-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22984,17 +22984,17 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -23018,13 +23018,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1209.77</v>
+        <v>1876.12</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4455-746-CM26</t>
+          <t>1272228-27-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23049,43 +23049,47 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>65.020.633-9</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>753.33</v>
+        <v>862.4400000000001</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2440-1631-CM26</t>
+          <t>4455-746-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23110,47 +23114,43 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1342.52</v>
+        <v>753.33</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>960857-13-CM26</t>
+          <t>2440-1631-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23175,27 +23175,27 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -23209,13 +23209,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1034.68</v>
+        <v>1342.52</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>951-60-CM26</t>
+          <t>960857-13-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23240,43 +23240,47 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>814.1900000000001</v>
+        <v>1034.68</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2440-1724-CM26</t>
+          <t>951-60-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23301,47 +23305,43 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2875.31</v>
+        <v>814.1900000000001</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1057384-807-CM26</t>
+          <t>2440-1724-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23366,47 +23366,47 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3069.23</v>
+        <v>2875.31</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1063538-7323-CM26</t>
+          <t>1057384-807-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23426,48 +23426,52 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>736.88</v>
+        <v>3069.23</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1627-1342-CM26</t>
+          <t>1063538-7323-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23487,32 +23491,32 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -23522,13 +23526,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>8491.57</v>
+        <v>736.88</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2440-1720-CM26</t>
+          <t>1627-1342-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23553,47 +23557,43 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>4480.1</v>
+        <v>8491.57</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5688-73-CM26</t>
+          <t>2440-1720-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23618,27 +23618,27 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -23652,13 +23652,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1896.15</v>
+        <v>4480.1</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>707415-113-CM26</t>
+          <t>5688-73-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23683,27 +23683,27 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -23717,13 +23717,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>742.14</v>
+        <v>1896.15</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3825-311-CM26</t>
+          <t>707415-113-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23748,32 +23748,32 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -23782,13 +23782,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1993.37</v>
+        <v>742.14</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1681-790-CM26</t>
+          <t>3825-311-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23813,32 +23813,32 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -23847,13 +23847,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>5959.1</v>
+        <v>1993.37</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1113015-96-CM26</t>
+          <t>1681-790-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23878,32 +23878,32 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -23912,13 +23912,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>857.24</v>
+        <v>5959.1</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1347772-96-CM26</t>
+          <t>1113015-96-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23943,43 +23943,47 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr"/>
+          <t>77.638.992-7</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1693.17</v>
+        <v>857.24</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3825-314-CM26</t>
+          <t>1347772-96-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24004,47 +24008,43 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2777.02</v>
+        <v>1693.17</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>960860-29-CM26</t>
+          <t>3825-314-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24069,27 +24069,27 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -24103,13 +24103,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2822.16</v>
+        <v>2777.02</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1057532-1698-CM26</t>
+          <t>960860-29-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -24134,17 +24134,17 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -24168,13 +24168,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>846.99</v>
+        <v>2822.16</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>998-283-CM26</t>
+          <t>1057532-1698-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24199,32 +24199,32 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2948.06</v>
+        <v>846.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>4179-1224-CM26</t>
+          <t>998-283-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24264,17 +24264,17 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>847.6799999999999</v>
+        <v>2948.06</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5740-392-CM26</t>
+          <t>4179-1224-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24329,32 +24329,32 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -24363,13 +24363,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>956.51</v>
+        <v>847.6799999999999</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1398-1369-CM26</t>
+          <t>5740-392-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24394,27 +24394,27 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -24428,13 +24428,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>13290.29</v>
+        <v>956.51</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1057472-14414-CM26</t>
+          <t>1398-1369-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24459,27 +24459,27 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.980.320-5</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2428.25</v>
+        <v>13290.29</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1662-2153-CM26</t>
+          <t>1057472-14414-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24524,27 +24524,27 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.602.273-3</t>
+          <t>61.980.320-5</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -24558,13 +24558,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>992.95</v>
+        <v>2428.25</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1057489-11808-CM26</t>
+          <t>1662-2153-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24589,32 +24589,32 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.602.273-3</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -24623,13 +24623,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>4416.08</v>
+        <v>992.95</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5740-393-CM26</t>
+          <t>1057489-11808-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24654,32 +24654,32 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>929.6900000000001</v>
+        <v>4416.08</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2393-1261-CM26</t>
+          <t>5740-393-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24719,27 +24719,27 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>69.254.900-7</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>3220.65</v>
+        <v>929.6900000000001</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2066-496-CM26</t>
+          <t>2393-1261-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24784,32 +24784,32 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>61.602.240-7</t>
+          <t>69.254.900-7</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Hospital Galvarino</t>
+          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>753.64</v>
+        <v>3220.65</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1050283-542-CM26</t>
+          <t>2066-496-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24849,32 +24849,32 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>61.602.240-7</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>Hospital Galvarino</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -24883,13 +24883,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1930.39</v>
+        <v>753.64</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1626-222-CM26</t>
+          <t>1050283-542-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24914,12 +24914,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24929,17 +24929,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -24948,13 +24948,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1507.66</v>
+        <v>1930.39</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1057429-2592-CM26</t>
+          <t>1626-222-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24979,43 +24979,47 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.602.201-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE CORONEL</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>7411.62</v>
+        <v>1507.66</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2019-84-CM26</t>
+          <t>1057429-2592-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25035,32 +25039,32 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.602.201-6</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE CORONEL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>76.176.425-k</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -25070,13 +25074,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1058.6</v>
+        <v>7411.62</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4623-21-CM26</t>
+          <t>2019-84-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25101,47 +25105,43 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2379.61</v>
+        <v>1058.6</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2080-10605-CM26</t>
+          <t>4623-21-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25166,32 +25166,32 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -25200,13 +25200,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>4570.68</v>
+        <v>2379.61</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1483311-12-CM26</t>
+          <t>2080-10605-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25231,17 +25231,17 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -25265,13 +25265,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2315.73</v>
+        <v>4570.68</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1233623-925-CM26</t>
+          <t>1483311-12-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25296,17 +25296,17 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -25330,13 +25330,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2772.43</v>
+        <v>2315.73</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1070620-9199-CM26</t>
+          <t>1233623-925-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25361,43 +25361,47 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>8109.99</v>
+        <v>2772.43</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1540-2295-CM26</t>
+          <t>1070620-9199-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25422,47 +25426,43 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>789.1900000000001</v>
+        <v>8109.99</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3553-476-CM26</t>
+          <t>1540-2295-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -25487,32 +25487,32 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25521,13 +25521,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1023.44</v>
+        <v>789.1900000000001</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1208099-24-CM26</t>
+          <t>3553-476-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25552,12 +25552,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25567,28 +25567,32 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Comercial IBL SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
-        </is>
-      </c>
-      <c r="K391" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>4164.59</v>
+        <v>1023.44</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>696954-89-CM26</t>
+          <t>1208099-24-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25613,47 +25617,43 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.452.485-3</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>903.37</v>
+        <v>4164.59</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>707412-75-CM26</t>
+          <t>696954-89-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25678,32 +25678,32 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -25712,13 +25712,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1782.22</v>
+        <v>903.37</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>3384-195-CM26</t>
+          <t>707412-75-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25743,32 +25743,32 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>81.448.600-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25777,13 +25777,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>855.2</v>
+        <v>1782.22</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1057547-15501-CM26</t>
+          <t>3384-195-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25808,27 +25808,27 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>81.448.600-1</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25842,13 +25842,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>6642.45</v>
+        <v>855.2</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2258-8185-CM26</t>
+          <t>1057547-15501-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25873,27 +25873,27 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -25907,13 +25907,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>12616.08</v>
+        <v>6642.45</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>520149-150-CM26</t>
+          <t>2258-8185-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25938,17 +25938,17 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -25972,13 +25972,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1735.55</v>
+        <v>12616.08</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>898-3444-CM26</t>
+          <t>520149-150-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26003,32 +26003,32 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -26037,13 +26037,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>15972.96</v>
+        <v>1735.55</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1057439-6481-CM26</t>
+          <t>898-3444-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26068,43 +26068,47 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K399" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>7053.91</v>
+        <v>15972.96</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2778-612-CM26</t>
+          <t>1057439-6481-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26129,47 +26133,43 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3382.35</v>
+        <v>7053.91</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2778-611-CM26</t>
+          <t>2778-612-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26209,17 +26209,17 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -26228,13 +26228,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3135.84</v>
+        <v>3382.35</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>928-326-CM26</t>
+          <t>2778-611-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26259,32 +26259,32 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -26293,13 +26293,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>745.05</v>
+        <v>3135.84</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4491-653-CM26</t>
+          <t>928-326-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -26324,43 +26324,47 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K403" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>833.11</v>
+        <v>745.05</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>935934-248-CM26</t>
+          <t>4491-653-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26385,47 +26389,43 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>69.150.501-4</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>1647.9</v>
+        <v>833.11</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2013-1683-CM26</t>
+          <t>935934-248-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26465,28 +26465,32 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K405" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>1369.95</v>
+        <v>1647.9</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1043046-112-CM26</t>
+          <t>2013-1683-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26511,47 +26515,43 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K406" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>732</v>
+        <v>1369.95</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>4819-127-CM26</t>
+          <t>1043046-112-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26576,32 +26576,32 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26610,13 +26610,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3079.35</v>
+        <v>732</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>3117-1498-CM26</t>
+          <t>4819-127-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26641,12 +26641,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26656,28 +26656,32 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MEGASTORE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>76.935.880-3</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>760.65</v>
+        <v>3079.35</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>4491-654-CM26</t>
+          <t>3117-1498-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26702,27 +26706,27 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>SOCIEDAD COMERCIAL MEGASTORE LIMITADA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
+          <t>76.935.880-3</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -26732,6 +26736,67 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
+        <v>760.65</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>4491-654-CM26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>69.150.501-4</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCO</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribuidora Colon </t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="n">
         <v>798.92</v>
       </c>
     </row>
